--- a/data/export/2026-10-14-182路.xlsx
+++ b/data/export/2026-10-14-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,17 +812,17 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -820,13 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,33 +931,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -998,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1048,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1100,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1109,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,17 +1161,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1153,13 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1413,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1524,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1500,22 +1532,22 @@
       <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>沪A13735A</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1548,12 +1580,12 @@
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1567,7 +1599,7 @@
       <c r="T10" s="2" t="inlineStr"/>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1603,7 +1635,792 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>2/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>1/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-182路.xlsx
+++ b/data/export/2026-10-14-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>78.0</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -870,36 +870,32 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -907,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -931,17 +927,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -951,17 +947,13 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -989,32 +981,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1022,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,17 +1042,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1066,13 +1062,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1110,24 +1110,24 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1219,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1252,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1276,33 +1280,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1330,32 +1338,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1363,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1387,33 +1399,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1513,7 +1529,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1524,7 +1540,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1624,7 +1640,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1635,7 +1651,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1663,32 +1679,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1696,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1720,33 +1740,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1857,7 +1881,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1942,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1972,7 +1996,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2057,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2083,7 +2107,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2168,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2194,7 +2218,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2279,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2299,17 +2323,13 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2317,22 +2337,22 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2370,7 +2390,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2384,43 +2404,955 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X17" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y17" s="2" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z17" s="2" t="inlineStr">
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr"/>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>—/13</t>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-182路.xlsx
+++ b/data/export/2026-10-14-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC25"/>
+  <dimension ref="A1:AC29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1689,24 +1689,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1765,12 +1765,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1909,32 +1909,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1942,7 +1946,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1966,37 +1970,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2024,32 +2028,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -2057,7 +2065,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2081,33 +2089,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2180,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2279,7 +2291,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2318,7 +2330,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2390,7 +2402,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2444,7 +2456,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2517,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2620,7 +2632,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2674,7 +2686,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2747,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2846,7 +2858,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2900,7 +2912,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2973,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3015,7 +3027,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3088,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,7 +3199,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3236,12 +3248,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3302,7 +3314,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3356,6 +3368,458 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-14-182路.xlsx
+++ b/data/export/2026-10-14-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC29"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,13 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1375,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1490,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1601,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1716,7 +1720,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1770,7 +1774,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1946,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2065,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2147,32 +2151,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2180,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2204,33 +2212,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2258,32 +2270,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2291,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2315,17 +2331,17 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2335,13 +2351,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2369,32 +2389,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2402,7 +2426,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2426,17 +2450,17 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2446,17 +2470,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2484,32 +2508,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2517,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2541,37 +2569,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2686,7 +2714,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2858,7 +2886,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2973,7 +3001,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,7 +3116,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,7 +3227,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3253,7 +3281,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3342,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,7 +3453,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3536,7 +3564,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3651,7 +3679,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3713,22 +3741,22 @@
       <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>沪A32298D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3761,12 +3789,12 @@
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3805,18 +3833,252 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
-      <c r="AC29" s="2" t="inlineStr">
-        <is>
-          <t>—/14</t>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-182路.xlsx
+++ b/data/export/2026-10-14-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>83.0</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,14 +1180,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>79.0</t>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,17 +1299,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,13 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1720,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1759,17 +1763,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1835,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1950,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1994,12 +1998,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2069,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2108,7 +2112,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2123,7 +2127,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2242,7 +2246,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2361,7 +2365,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2465,14 +2469,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>83.0</t>
@@ -2480,7 +2484,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2599,7 +2603,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2627,32 +2631,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2660,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2684,29 +2692,29 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>79.0</t>
@@ -2714,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,7 +2822,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2853,32 +2861,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -2886,7 +2898,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2910,32 +2922,32 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -2968,32 +2980,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3001,7 +3017,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3025,37 +3041,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3083,32 +3099,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -3116,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3140,17 +3160,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3160,13 +3180,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3194,32 +3218,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3227,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3251,32 +3279,32 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3342,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3381,7 +3409,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3453,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3531,32 +3559,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3564,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3588,17 +3620,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3608,12 +3640,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3679,7 +3711,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3718,7 +3750,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3733,7 +3765,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3794,7 +3826,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3848,7 +3880,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3941,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3963,7 +3995,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3971,22 +4003,22 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4024,7 +4056,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4038,47 +4070,959 @@
       <c r="T31" s="2" t="inlineStr"/>
       <c r="U31" s="2" t="inlineStr">
         <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W31" s="2" t="inlineStr">
+      <c r="W32" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X31" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y31" s="2" t="inlineStr">
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z31" s="2" t="inlineStr">
+      <c r="Z32" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
+      <c r="AA32" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
+      <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>89.5</t>
         </is>
       </c>
-      <c r="AC31" s="2" t="inlineStr">
-        <is>
-          <t>6/14</t>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>93.5</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-182路.xlsx
+++ b/data/export/2026-10-14-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>81.3</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,17 +942,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,22 +1299,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1883,13 +1883,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1993,14 +1997,14 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>81.3</t>
@@ -2008,7 +2012,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2117,17 +2121,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2231,17 +2235,17 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2311,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2350,17 +2354,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2430,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2474,17 +2478,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2588,17 +2592,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2668,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2712,17 +2716,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2822,7 +2826,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2898,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2937,22 +2941,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3071,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3309,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3448,32 +3452,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3481,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3505,17 +3513,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3525,13 +3533,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3635,14 +3647,14 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
           <t>81.3</t>
@@ -3650,7 +3662,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3678,32 +3690,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -3711,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3735,17 +3751,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3755,17 +3771,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3793,32 +3809,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -3826,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3850,32 +3870,32 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3908,32 +3928,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3941,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3965,32 +3989,32 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4023,32 +4047,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4056,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4080,17 +4108,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4100,17 +4128,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4138,32 +4166,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4171,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4195,32 +4227,32 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4253,32 +4285,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4286,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4310,17 +4346,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4330,17 +4366,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4440,7 +4476,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4479,32 +4515,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -4512,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4536,37 +4576,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4667,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4681,7 +4721,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4796,7 +4836,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4897,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4915,22 +4955,22 @@
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>沪A66513D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -4963,12 +5003,12 @@
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4982,47 +5022,733 @@
       <c r="T39" s="2" t="inlineStr"/>
       <c r="U39" s="2" t="inlineStr">
         <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W39" s="2" t="inlineStr">
+      <c r="W40" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X39" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y39" s="2" t="inlineStr">
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z39" s="2" t="inlineStr">
+      <c r="Z40" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>7/14</t>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>78.3</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-182路.xlsx
+++ b/data/export/2026-10-14-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC45"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>81.3</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,17 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,22 +1180,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2002,17 +2002,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,17 +2359,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,14 +2473,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>81.3</t>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,22 +2711,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2831,13 +2831,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2951,12 +2955,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3065,17 +3069,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3303,17 +3307,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3413,7 +3417,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3489,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3528,7 +3532,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3543,7 +3547,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3652,17 +3656,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,7 +3770,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3846,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,7 +3889,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3900,7 +3904,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4009,17 +4013,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4123,14 +4127,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>81.3</t>
@@ -4138,7 +4142,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4257,7 +4261,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4295,24 +4299,24 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4322,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4361,22 +4365,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4404,32 +4408,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -4437,7 +4445,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4461,17 +4469,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4481,13 +4489,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB34" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -4525,12 +4537,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -4552,7 +4564,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4601,12 +4613,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4634,32 +4646,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4667,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4691,17 +4707,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4711,17 +4727,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4749,32 +4765,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4782,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4806,17 +4826,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4826,17 +4846,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4936,7 +4956,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4975,32 +4995,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5008,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5032,17 +5056,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5052,17 +5076,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5147,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5162,7 +5186,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5205,32 +5229,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5238,7 +5266,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5262,17 +5290,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5282,17 +5310,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5353,7 +5381,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5392,7 +5420,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5407,7 +5435,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5496,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5522,7 +5550,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5583,7 +5611,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5627,13 +5655,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB44" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -5694,7 +5726,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5743,10 +5775,696 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
           <t>78.3</t>
         </is>
       </c>
-      <c r="AC45" s="2" t="inlineStr">
+      <c r="AC51" s="2" t="inlineStr">
         <is>
           <t>4/14</t>
         </is>

--- a/data/export/2026-10-14-182路.xlsx
+++ b/data/export/2026-10-14-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,14 +1418,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,13 +1653,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,14 +1767,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>88.7</t>
@@ -1778,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1878,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2077,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2131,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2240,17 +2244,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2364,12 +2368,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2488,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2597,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2726,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2826,22 +2830,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2950,12 +2954,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3025,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3064,14 +3068,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -3079,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3302,14 +3306,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>88.7</t>
@@ -3317,7 +3321,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3422,13 +3426,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3532,22 +3540,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3731,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3785,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3894,17 +3902,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4018,12 +4026,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4142,7 +4150,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4251,17 +4259,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4380,7 +4388,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4484,22 +4492,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4608,12 +4616,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4683,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4722,14 +4730,14 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -4737,7 +4745,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4841,14 +4849,14 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
           <t>88.7</t>
@@ -4856,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4961,13 +4969,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB38" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5017,12 +5029,12 @@
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5032,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5147,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5201,7 +5213,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5239,24 +5251,24 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5266,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5315,12 +5327,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5348,32 +5360,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5381,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5405,17 +5421,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5425,17 +5441,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5463,32 +5479,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5496,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5520,17 +5540,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5540,17 +5560,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5578,32 +5598,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -5611,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5635,37 +5659,37 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5693,32 +5717,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -5726,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5750,17 +5778,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5770,12 +5798,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5808,32 +5836,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -5841,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5865,17 +5897,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5885,13 +5917,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5919,32 +5955,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5952,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5976,37 +6016,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6067,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6121,7 +6161,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6222,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6236,7 +6276,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6297,7 +6337,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6341,17 +6381,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6412,7 +6452,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6466,7 +6506,467 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>69.5</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
           <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-182路.xlsx
+++ b/data/export/2026-10-14-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>79.2</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>79.2</t>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2125,17 +2125,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2244,17 +2244,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,22 +2477,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3659,14 +3659,14 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
           <t>79.2</t>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3902,17 +3902,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4135,22 +4135,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5083,14 +5083,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>79.2</t>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5203,17 +5203,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5441,17 +5441,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5727,24 +5727,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5846,12 +5846,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5965,24 +5965,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6074,32 +6074,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -6107,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6131,17 +6135,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6151,17 +6155,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6189,32 +6193,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6222,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6246,37 +6254,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6304,32 +6312,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -6337,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6361,17 +6373,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6381,17 +6393,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6491,7 +6503,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6567,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6682,7 +6694,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6736,7 +6748,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6797,7 +6809,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6846,7 +6858,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6912,7 +6924,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6970,6 +6982,466 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>79.2</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>78.3</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-14-182路.xlsx
+++ b/data/export/2026-10-14-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,17 +2482,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4140,17 +4140,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4378,12 +4378,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6193,36 +6193,32 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6230,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6254,17 +6250,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6274,17 +6270,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6431,32 +6427,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6488,17 +6488,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7083,17 +7083,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7428,17 +7428,247 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB59" s="2" t="inlineStr">
-        <is>
-          <t>78.3</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr">
-        <is>
-          <t>6/14</t>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-182路.xlsx
+++ b/data/export/2026-10-14-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,14 +1061,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>79.2</t>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,14 +1299,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>78.5</t>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,17 +1767,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1887,17 +1887,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>79.2</t>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,12 +2835,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>78.5</t>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,17 +3073,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,17 +3306,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3545,17 +3545,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3659,22 +3659,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4254,14 +4254,14 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>79.2</t>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4611,14 +4611,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>78.5</t>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4849,17 +4849,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5083,22 +5083,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5555,14 +5555,14 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>79.2</t>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5793,14 +5793,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>78.5</t>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6036,17 +6036,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6318,24 +6318,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6546,32 +6546,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -6579,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6603,17 +6607,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6623,12 +6627,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6661,32 +6665,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6694,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6718,17 +6726,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6738,17 +6746,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6776,32 +6784,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6809,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6833,17 +6845,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6853,17 +6865,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6891,32 +6903,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6924,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6948,32 +6964,32 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7006,32 +7022,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7039,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7063,17 +7083,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7083,12 +7103,12 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7121,32 +7141,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7154,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7178,37 +7202,37 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7308,7 +7332,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7384,7 +7408,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7433,7 +7457,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7499,7 +7523,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7553,7 +7577,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7614,7 +7638,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7658,17 +7682,707 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>83.8</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>79.2</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-182路.xlsx
+++ b/data/export/2026-10-14-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC67"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,22 +1299,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2720,17 +2720,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,22 +2949,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,22 +4016,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4378,17 +4378,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4611,22 +4611,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5093,12 +5093,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5317,22 +5317,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6508,17 +6508,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7032,24 +7032,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7227,12 +7227,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7260,32 +7260,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -7293,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7317,17 +7321,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7337,12 +7341,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7375,32 +7379,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7408,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7432,17 +7440,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7452,17 +7460,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7490,32 +7498,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7523,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7547,37 +7559,37 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7605,32 +7617,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7638,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7662,17 +7678,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7682,7 +7698,7 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
@@ -7692,7 +7708,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7720,32 +7736,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -7753,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7777,37 +7797,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7983,7 +8003,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8022,7 +8042,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8037,7 +8057,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8118,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8147,12 +8167,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8233,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8275,22 +8295,22 @@
       <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>沪A02126A</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8323,12 +8343,12 @@
       <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8342,47 +8362,852 @@
       <c r="T67" s="2" t="inlineStr"/>
       <c r="U67" s="2" t="inlineStr">
         <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
           <t>16:20</t>
         </is>
       </c>
-      <c r="V67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W67" s="2" t="inlineStr">
+      <c r="W68" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X67" s="2" t="inlineStr">
+      <c r="X68" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y67" s="2" t="inlineStr">
+      <c r="Y68" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z67" s="2" t="inlineStr">
+      <c r="Z68" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr">
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
         <is>
           <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>75.3</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>79.2</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-182路.xlsx
+++ b/data/export/2026-10-14-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,17 +1648,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3659,22 +3659,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4730,22 +4730,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4964,17 +4964,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5083,22 +5083,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5560,17 +5560,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5912,17 +5912,17 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6741,22 +6741,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7217,22 +7217,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7627,24 +7627,24 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7693,22 +7693,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7746,24 +7746,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7927,7 +7927,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7970,32 +7970,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8003,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8027,17 +8031,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8047,17 +8051,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8085,32 +8089,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8118,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8142,37 +8150,37 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8200,32 +8208,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -8233,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8257,32 +8269,32 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8348,7 +8360,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8387,7 +8399,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8463,7 +8475,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8578,7 +8590,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8617,7 +8629,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8693,7 +8705,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8808,7 +8820,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8923,7 +8935,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8985,22 +8997,22 @@
       <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>沪A68397D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9033,12 +9045,12 @@
       <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9087,12 +9099,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9100,7 +9112,7 @@
       <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -9110,7 +9122,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -9148,12 +9160,12 @@
       <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9167,47 +9179,967 @@
       <c r="T74" s="2" t="inlineStr"/>
       <c r="U74" s="2" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="V74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W74" s="2" t="inlineStr">
+      <c r="W75" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X74" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y74" s="2" t="inlineStr">
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z74" s="2" t="inlineStr">
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>70.3</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>79.4</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB74" s="2" t="inlineStr">
-        <is>
-          <t>79.2</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr">
-        <is>
-          <t>12/14</t>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>83.8</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>75.3</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>77.7</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-182路.xlsx
+++ b/data/export/2026-10-14-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,22 +1180,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,22 +1299,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1887,17 +1887,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,22 +2239,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,17 +2477,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,22 +2715,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,22 +2949,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3192,17 +3192,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3545,17 +3545,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3897,22 +3897,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,22 +4016,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4135,17 +4135,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4373,22 +4373,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4611,22 +4611,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5317,22 +5317,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5436,22 +5436,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5560,17 +5560,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6036,17 +6036,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6265,17 +6265,17 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6384,22 +6384,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6503,22 +6503,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7098,17 +7098,17 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7341,17 +7341,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7455,22 +7455,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7574,22 +7574,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8051,17 +8051,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8442,32 +8442,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -8475,7 +8479,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8499,17 +8503,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8519,17 +8523,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -8557,32 +8561,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8590,7 +8598,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8614,17 +8622,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8634,17 +8642,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8672,32 +8680,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8705,7 +8717,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8729,32 +8741,32 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8787,32 +8799,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8820,7 +8836,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8844,37 +8860,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8902,32 +8918,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -8935,7 +8955,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8959,37 +8979,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9017,32 +9037,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9050,7 +9074,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9074,37 +9098,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9132,32 +9156,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -9165,7 +9193,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9189,37 +9217,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9280,7 +9308,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9319,7 +9347,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9334,7 +9362,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -9362,32 +9390,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9395,7 +9427,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9419,17 +9451,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9439,17 +9471,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9542,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9564,7 +9596,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9625,7 +9657,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9664,7 +9696,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9740,7 +9772,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9855,7 +9887,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9970,7 +10002,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10014,17 +10046,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10032,22 +10064,22 @@
       <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>沪A67353D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -10085,7 +10117,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10129,17 +10161,822 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB82" s="2" t="inlineStr">
+      <c r="AB83" s="2" t="inlineStr">
         <is>
           <t>77.7</t>
         </is>
       </c>
-      <c r="AC82" s="2" t="inlineStr">
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
         <is>
           <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>70.3</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-182路.xlsx
+++ b/data/export/2026-10-14-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC89"/>
+  <dimension ref="A1:AC94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,17 +1767,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1887,17 +1887,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,22 +2120,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,17 +2835,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,17 +3306,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3426,17 +3426,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3545,17 +3545,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3659,22 +3659,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,22 +3778,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4497,17 +4497,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4730,22 +4730,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4849,17 +4849,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5083,22 +5083,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5198,22 +5198,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5565,12 +5565,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5679,17 +5679,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5917,17 +5917,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6036,17 +6036,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6150,22 +6150,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6627,17 +6627,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6741,22 +6741,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7217,22 +7217,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7465,12 +7465,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7693,22 +7693,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7927,17 +7927,17 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8165,22 +8165,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8289,17 +8289,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8399,22 +8399,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8642,17 +8642,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8717,7 +8717,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9047,24 +9047,24 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9166,24 +9166,24 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9275,32 +9275,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -9308,7 +9312,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9332,17 +9336,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9352,17 +9356,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9400,24 +9404,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9427,7 +9431,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9476,12 +9480,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9509,32 +9513,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9542,7 +9550,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9566,37 +9574,37 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9624,32 +9632,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -9657,7 +9669,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9681,17 +9693,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9701,17 +9713,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9739,32 +9751,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -9772,7 +9788,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9796,37 +9812,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9854,32 +9870,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9887,7 +9907,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9911,32 +9931,32 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -9969,32 +9989,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10002,7 +10026,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10026,17 +10050,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10046,17 +10070,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -10117,7 +10141,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10199,32 +10223,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10232,7 +10260,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10256,37 +10284,37 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -10347,7 +10375,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10401,7 +10429,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10462,7 +10490,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10501,7 +10529,7 @@
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
@@ -10516,7 +10544,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10577,7 +10605,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10626,12 +10654,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10720,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10736,17 +10764,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10807,7 +10835,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10856,12 +10884,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10869,22 +10897,22 @@
       <c r="A89" s="2" t="inlineStr"/>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -10917,12 +10945,12 @@
       <c r="M89" s="2" t="inlineStr"/>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10936,47 +10964,622 @@
       <c r="T89" s="2" t="inlineStr"/>
       <c r="U89" s="2" t="inlineStr">
         <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="V89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W89" s="2" t="inlineStr">
+      <c r="W90" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X89" s="2" t="inlineStr">
+      <c r="X90" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y89" s="2" t="inlineStr">
+      <c r="Y90" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z89" s="2" t="inlineStr">
+      <c r="Z90" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA89" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB89" s="2" t="inlineStr">
-        <is>
-          <t>74.5</t>
-        </is>
-      </c>
-      <c r="AC89" s="2" t="inlineStr">
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>78.1</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
         <is>
           <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-182路.xlsx
+++ b/data/export/2026-10-14-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC94"/>
+  <dimension ref="A1:AC95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8761,12 +8761,12 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9312,7 +9312,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9550,7 +9550,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9999,24 +9999,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10108,32 +10108,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10141,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10165,17 +10169,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10185,12 +10189,12 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10260,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10375,7 +10379,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10490,7 +10494,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10605,7 +10609,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10720,7 +10724,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10835,7 +10839,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10874,7 +10878,7 @@
       </c>
       <c r="Z88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA88" s="2" t="inlineStr">
@@ -10950,7 +10954,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11065,7 +11069,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11180,7 +11184,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11295,7 +11299,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11410,7 +11414,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11525,7 +11529,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11583,6 +11587,121 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:41</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-14-182路.xlsx
+++ b/data/export/2026-10-14-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC95"/>
+  <dimension ref="A1:AC97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,17 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,22 +1648,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,12 +2835,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,17 +3073,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3421,22 +3421,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4964,22 +4964,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5322,17 +5322,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5912,22 +5912,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6746,17 +6746,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7579,17 +7579,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7698,17 +7698,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7817,17 +7817,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8284,22 +8284,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8880,17 +8880,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9009,7 +9009,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9356,12 +9356,12 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9594,17 +9594,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9669,7 +9669,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9708,22 +9708,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10494,7 +10498,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10518,17 +10522,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10538,17 +10542,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10609,7 +10613,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10663,7 +10667,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10691,32 +10695,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -10724,7 +10732,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10748,17 +10756,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10768,12 +10776,12 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10806,32 +10814,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -10839,7 +10851,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10863,17 +10875,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10883,17 +10895,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10921,32 +10933,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10954,7 +10970,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10978,17 +10994,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -10998,17 +11014,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -11069,7 +11085,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11151,32 +11167,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -11184,7 +11204,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11208,37 +11228,37 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11319,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11414,7 +11434,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11453,7 +11473,7 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11529,7 +11549,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11573,17 +11593,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -11644,7 +11664,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11688,17 +11708,247 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
           <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-182路.xlsx
+++ b/data/export/2026-10-14-182路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,17 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3783,12 +3783,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5322,17 +5322,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7579,17 +7579,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7817,17 +7817,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7932,12 +7932,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8294,12 +8294,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8880,17 +8880,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9009,7 +9009,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9669,7 +9669,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9718,12 +9718,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9832,12 +9832,12 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9951,12 +9951,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10308,12 +10308,12 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10542,17 +10542,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -10667,7 +10667,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10895,17 +10895,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11052,32 +11052,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11085,7 +11089,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11109,17 +11113,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11129,12 +11133,12 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11177,12 +11181,12 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
@@ -11204,7 +11208,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11253,12 +11257,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11286,32 +11290,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11319,7 +11327,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11343,17 +11351,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11363,12 +11371,12 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11401,32 +11409,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11434,7 +11446,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11458,17 +11470,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11478,12 +11490,12 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
@@ -11516,32 +11528,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11549,7 +11565,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11573,17 +11589,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11593,17 +11609,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -11631,32 +11647,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -11664,7 +11684,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11688,17 +11708,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11708,17 +11728,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11799,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11828,12 +11848,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11914,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11938,12 +11958,12 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">

--- a/data/export/2026-10-14-182路.xlsx
+++ b/data/export/2026-10-14-182路.xlsx
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2125,17 +2125,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3426,17 +3426,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5203,17 +5203,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5917,17 +5917,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6155,17 +6155,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8289,17 +8289,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8404,17 +8404,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9669,7 +9669,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9832,17 +9832,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10667,7 +10667,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -11208,7 +11208,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11252,17 +11252,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11490,17 +11490,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>21:43</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
@@ -11684,7 +11684,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11733,12 +11733,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -11766,32 +11766,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -11799,7 +11803,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11823,17 +11827,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11843,17 +11847,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11881,32 +11885,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11914,7 +11922,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11938,17 +11946,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11958,17 +11966,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
